--- a/relatorio_impressoras.xlsx
+++ b/relatorio_impressoras.xlsx
@@ -117,7 +117,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ultima verificacao: 30/04/2026 11:27:41</t>
+          <t>Ultima verificacao: 30/04/2026 12:07:51</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C27" t="inlineStr" s="1">
         <is>
-          <t>68%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="1">
@@ -904,7 +904,7 @@
       </c>
       <c r="C35" t="inlineStr" s="1">
         <is>
-          <t>98%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="1">

--- a/relatorio_impressoras.xlsx
+++ b/relatorio_impressoras.xlsx
@@ -117,7 +117,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ultima verificacao: 30/04/2026 12:07:51</t>
+          <t>Ultima verificacao: 30/04/2026 13:34:33</t>
         </is>
       </c>
     </row>
